--- a/data/b2_centro/B2 Centro 07-2026.xlsx
+++ b/data/b2_centro/B2 Centro 07-2026.xlsx
@@ -5013,20 +5013,20 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>2371.59</v>
+        <v>77643.03</v>
       </c>
     </row>
     <row r="3">
@@ -5035,16 +5035,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>79585.35000000001</v>
+        <v>1597.54</v>
       </c>
     </row>
     <row r="4">
@@ -5062,25 +5062,25 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>4187.41</v>
+        <v>4062.12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3169.42</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="6">
@@ -5089,16 +5089,16 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>38000</v>
+        <v>4414.07</v>
       </c>
     </row>
     <row r="7">
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>5722.86</v>
+        <v>6017.76</v>
       </c>
     </row>
     <row r="9">
@@ -5152,25 +5152,25 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1874.41</v>
+        <v>1947.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1164.44</v>
+        <v>13387.16</v>
       </c>
     </row>
     <row r="11">
@@ -5179,39 +5179,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>13941.94</v>
+        <v>4091.55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>4512.74</v>
+        <v>1267.64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46221</v>
+        <v>46219</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -5220,65 +5220,65 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1738.84</v>
+        <v>1985.59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46222</v>
+        <v>46220</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>5707.72</v>
+        <v>2970.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46223</v>
+        <v>46222</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>27975.81</v>
+        <v>5933.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46226</v>
+        <v>46223</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>953.04</v>
+        <v>27583.42</v>
       </c>
     </row>
     <row r="17">
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>5500.34</v>
+        <v>5665.92</v>
       </c>
     </row>
     <row r="18">
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>4059.15</v>
+        <v>4128.65</v>
       </c>
     </row>
   </sheetData>
